--- a/data/tables/table_selection_analysis.xlsx
+++ b/data/tables/table_selection_analysis.xlsx
@@ -1,25 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10209"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gelana.khazeeva/Dropbox/450k/Manuscript/Final submissiion/tables/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4849F8-D5AD-454F-ABB4-8DDA9C9AF169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20500" yWindow="-21600" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Raw data" sheetId="1" r:id="rId1"/>
     <sheet name="Paper table" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Paper table'!$B$2:$AC$16</definedName>
-  </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -791,8 +782,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -803,21 +794,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -859,39 +835,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -929,7 +890,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -963,7 +924,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -998,10 +958,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1174,86 +1133,86 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:BM27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:65">
       <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="2"/>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="2" t="s">
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
-      <c r="AK1" s="2"/>
-      <c r="AL1" s="2"/>
-      <c r="AM1" s="2"/>
-      <c r="AN1" s="2"/>
-      <c r="AO1" s="2"/>
-      <c r="AP1" s="2"/>
-      <c r="AQ1" s="2"/>
-      <c r="AR1" s="2"/>
-      <c r="AS1" s="2"/>
-      <c r="AT1" s="2"/>
-      <c r="AU1" s="2"/>
-      <c r="AV1" s="2"/>
-      <c r="AW1" s="2"/>
-      <c r="AX1" s="2" t="s">
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="1"/>
+      <c r="AX1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="AY1" s="2"/>
-      <c r="AZ1" s="2"/>
-      <c r="BA1" s="2"/>
-      <c r="BB1" s="2"/>
-      <c r="BC1" s="2"/>
-      <c r="BD1" s="2"/>
-      <c r="BE1" s="2"/>
-      <c r="BF1" s="2"/>
-      <c r="BG1" s="2"/>
-      <c r="BH1" s="2"/>
-      <c r="BI1" s="2"/>
-      <c r="BJ1" s="2"/>
-      <c r="BK1" s="2"/>
-      <c r="BL1" s="2"/>
-      <c r="BM1" s="2"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
     </row>
-    <row r="2" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:65">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>4</v>
@@ -1448,8 +1407,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:65" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:65" hidden="1"/>
+    <row r="4" spans="1:65">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1457,13 +1416,13 @@
         <v>20</v>
       </c>
       <c r="C4">
-        <v>1.360537152513525E-4</v>
+        <v>0.0001360537152513525</v>
       </c>
       <c r="D4">
-        <v>1.0001360629709779</v>
+        <v>1.000136062970978</v>
       </c>
       <c r="E4">
-        <v>0.97770224547265538</v>
+        <v>0.9777022454726554</v>
       </c>
       <c r="F4">
         <v>1.023084634495772</v>
@@ -1475,10 +1434,10 @@
         <v>42</v>
       </c>
       <c r="I4">
-        <v>0.98767493397003503</v>
+        <v>0.987674933970035</v>
       </c>
       <c r="J4">
-        <v>9.8767493397003499</v>
+        <v>9.87674933970035</v>
       </c>
       <c r="K4">
         <v>10</v>
@@ -1505,13 +1464,13 @@
         <v>20</v>
       </c>
       <c r="S4">
-        <v>1.360537152513525E-4</v>
+        <v>0.0001360537152513525</v>
       </c>
       <c r="T4">
-        <v>1.0001360629709779</v>
+        <v>1.000136062970978</v>
       </c>
       <c r="U4">
-        <v>0.97770224547265538</v>
+        <v>0.9777022454726554</v>
       </c>
       <c r="V4">
         <v>1.023084634495772</v>
@@ -1523,10 +1482,10 @@
         <v>42</v>
       </c>
       <c r="Y4">
-        <v>0.98767493397003503</v>
+        <v>0.987674933970035</v>
       </c>
       <c r="Z4">
-        <v>9.8767493397003499</v>
+        <v>9.87674933970035</v>
       </c>
       <c r="AA4">
         <v>10</v>
@@ -1553,13 +1512,13 @@
         <v>20</v>
       </c>
       <c r="AI4">
-        <v>1.360537152513525E-4</v>
+        <v>0.0001360537152513525</v>
       </c>
       <c r="AJ4">
-        <v>1.0001360629709779</v>
+        <v>1.000136062970978</v>
       </c>
       <c r="AK4">
-        <v>0.97770224547265538</v>
+        <v>0.9777022454726554</v>
       </c>
       <c r="AL4">
         <v>1.023084634495772</v>
@@ -1571,10 +1530,10 @@
         <v>42</v>
       </c>
       <c r="AO4">
-        <v>0.98767493397003503</v>
+        <v>0.987674933970035</v>
       </c>
       <c r="AP4">
-        <v>9.8767493397003499</v>
+        <v>9.87674933970035</v>
       </c>
       <c r="AQ4">
         <v>10</v>
@@ -1601,13 +1560,13 @@
         <v>20</v>
       </c>
       <c r="AY4">
-        <v>1.360537152513525E-4</v>
+        <v>0.0001360537152513525</v>
       </c>
       <c r="AZ4">
-        <v>1.0001360629709779</v>
+        <v>1.000136062970978</v>
       </c>
       <c r="BA4">
-        <v>0.97770224547265538</v>
+        <v>0.9777022454726554</v>
       </c>
       <c r="BB4">
         <v>1.023084634495772</v>
@@ -1619,10 +1578,10 @@
         <v>42</v>
       </c>
       <c r="BE4">
-        <v>0.98767493397003503</v>
+        <v>0.987674933970035</v>
       </c>
       <c r="BF4">
-        <v>9.8767493397003499</v>
+        <v>9.87674933970035</v>
       </c>
       <c r="BG4">
         <v>10</v>
@@ -1646,7 +1605,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:65">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1654,16 +1613,16 @@
         <v>21</v>
       </c>
       <c r="C5">
-        <v>-2.958521284869969E-2</v>
+        <v>-0.02958521284869969</v>
       </c>
       <c r="D5">
-        <v>0.97084814538019581</v>
+        <v>0.9708481453801958</v>
       </c>
       <c r="E5">
-        <v>0.95230044965750815</v>
+        <v>0.9523004496575082</v>
       </c>
       <c r="F5">
-        <v>0.98975708950589036</v>
+        <v>0.9897570895058904</v>
       </c>
       <c r="G5" t="s">
         <v>27</v>
@@ -1672,10 +1631,10 @@
         <v>43</v>
       </c>
       <c r="I5">
-        <v>7.7931412518559496E-5</v>
+        <v>7.79314125185595E-05</v>
       </c>
       <c r="J5">
-        <v>7.7931412518559499E-4</v>
+        <v>0.000779314125185595</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -1702,16 +1661,16 @@
         <v>21</v>
       </c>
       <c r="S5">
-        <v>-2.958521284869969E-2</v>
+        <v>-0.02958521284869969</v>
       </c>
       <c r="T5">
-        <v>0.97084814538019581</v>
+        <v>0.9708481453801958</v>
       </c>
       <c r="U5">
-        <v>0.95230044965750815</v>
+        <v>0.9523004496575082</v>
       </c>
       <c r="V5">
-        <v>0.98975708950589036</v>
+        <v>0.9897570895058904</v>
       </c>
       <c r="W5" t="s">
         <v>27</v>
@@ -1720,10 +1679,10 @@
         <v>43</v>
       </c>
       <c r="Y5">
-        <v>7.7931412518559496E-5</v>
+        <v>7.79314125185595E-05</v>
       </c>
       <c r="Z5">
-        <v>7.7931412518559499E-4</v>
+        <v>0.000779314125185595</v>
       </c>
       <c r="AA5">
         <v>10</v>
@@ -1750,16 +1709,16 @@
         <v>21</v>
       </c>
       <c r="AI5">
-        <v>-2.958521284869969E-2</v>
+        <v>-0.02958521284869969</v>
       </c>
       <c r="AJ5">
-        <v>0.97084814538019581</v>
+        <v>0.9708481453801958</v>
       </c>
       <c r="AK5">
-        <v>0.95230044965750815</v>
+        <v>0.9523004496575082</v>
       </c>
       <c r="AL5">
-        <v>0.98975708950589036</v>
+        <v>0.9897570895058904</v>
       </c>
       <c r="AM5" t="s">
         <v>27</v>
@@ -1768,10 +1727,10 @@
         <v>43</v>
       </c>
       <c r="AO5">
-        <v>7.7931412518559496E-5</v>
+        <v>7.79314125185595E-05</v>
       </c>
       <c r="AP5">
-        <v>7.7931412518559499E-4</v>
+        <v>0.000779314125185595</v>
       </c>
       <c r="AQ5">
         <v>10</v>
@@ -1798,16 +1757,16 @@
         <v>21</v>
       </c>
       <c r="AY5">
-        <v>-2.958521284869969E-2</v>
+        <v>-0.02958521284869969</v>
       </c>
       <c r="AZ5">
-        <v>0.97084814538019581</v>
+        <v>0.9708481453801958</v>
       </c>
       <c r="BA5">
-        <v>0.95230044965750815</v>
+        <v>0.9523004496575082</v>
       </c>
       <c r="BB5">
-        <v>0.98975708950589036</v>
+        <v>0.9897570895058904</v>
       </c>
       <c r="BC5" t="s">
         <v>27</v>
@@ -1816,10 +1775,10 @@
         <v>43</v>
       </c>
       <c r="BE5">
-        <v>7.7931412518559496E-5</v>
+        <v>7.79314125185595E-05</v>
       </c>
       <c r="BF5">
-        <v>7.7931412518559499E-4</v>
+        <v>0.000779314125185595</v>
       </c>
       <c r="BG5">
         <v>10</v>
@@ -1843,7 +1802,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:65">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1851,13 +1810,13 @@
         <v>22</v>
       </c>
       <c r="C6">
-        <v>3.490803688521258E-3</v>
+        <v>0.003490803688521258</v>
       </c>
       <c r="D6">
         <v>1.003496903639562</v>
       </c>
       <c r="E6">
-        <v>0.98734061358121217</v>
+        <v>0.9873406135812122</v>
       </c>
       <c r="F6">
         <v>1.019917566200025</v>
@@ -1869,10 +1828,10 @@
         <v>44</v>
       </c>
       <c r="I6">
-        <v>0.57958985783333761</v>
+        <v>0.5795898578333376</v>
       </c>
       <c r="J6">
-        <v>5.7958985783333761</v>
+        <v>5.795898578333376</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -1899,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="S6">
-        <v>3.490803688521258E-3</v>
+        <v>0.003490803688521258</v>
       </c>
       <c r="T6">
         <v>1.003496903639562</v>
       </c>
       <c r="U6">
-        <v>0.98734061358121217</v>
+        <v>0.9873406135812122</v>
       </c>
       <c r="V6">
         <v>1.019917566200025</v>
@@ -1917,10 +1876,10 @@
         <v>44</v>
       </c>
       <c r="Y6">
-        <v>0.57958985783333761</v>
+        <v>0.5795898578333376</v>
       </c>
       <c r="Z6">
-        <v>5.7958985783333761</v>
+        <v>5.795898578333376</v>
       </c>
       <c r="AA6">
         <v>10</v>
@@ -1947,13 +1906,13 @@
         <v>22</v>
       </c>
       <c r="AI6">
-        <v>3.490803688521258E-3</v>
+        <v>0.003490803688521258</v>
       </c>
       <c r="AJ6">
         <v>1.003496903639562</v>
       </c>
       <c r="AK6">
-        <v>0.98734061358121217</v>
+        <v>0.9873406135812122</v>
       </c>
       <c r="AL6">
         <v>1.019917566200025</v>
@@ -1965,10 +1924,10 @@
         <v>44</v>
       </c>
       <c r="AO6">
-        <v>0.57958985783333761</v>
+        <v>0.5795898578333376</v>
       </c>
       <c r="AP6">
-        <v>5.7958985783333761</v>
+        <v>5.795898578333376</v>
       </c>
       <c r="AQ6">
         <v>10</v>
@@ -1995,13 +1954,13 @@
         <v>22</v>
       </c>
       <c r="AY6">
-        <v>3.490803688521258E-3</v>
+        <v>0.003490803688521258</v>
       </c>
       <c r="AZ6">
         <v>1.003496903639562</v>
       </c>
       <c r="BA6">
-        <v>0.98734061358121217</v>
+        <v>0.9873406135812122</v>
       </c>
       <c r="BB6">
         <v>1.019917566200025</v>
@@ -2013,10 +1972,10 @@
         <v>44</v>
       </c>
       <c r="BE6">
-        <v>0.57958985783333761</v>
+        <v>0.5795898578333376</v>
       </c>
       <c r="BF6">
-        <v>5.7958985783333761</v>
+        <v>5.795898578333376</v>
       </c>
       <c r="BG6">
         <v>10</v>
@@ -2040,7 +1999,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:65">
       <c r="A7" s="1">
         <v>2</v>
       </c>
@@ -2048,16 +2007,16 @@
         <v>21</v>
       </c>
       <c r="C7">
-        <v>-2.957987637108872E-2</v>
+        <v>-0.02957987637108872</v>
       </c>
       <c r="D7">
-        <v>0.97085332630341126</v>
+        <v>0.9708533263034113</v>
       </c>
       <c r="E7">
-        <v>0.95230553065076895</v>
+        <v>0.9523055306507689</v>
       </c>
       <c r="F7">
-        <v>0.98976237232423858</v>
+        <v>0.9897623723242386</v>
       </c>
       <c r="G7" t="s">
         <v>27</v>
@@ -2066,10 +2025,10 @@
         <v>43</v>
       </c>
       <c r="I7">
-        <v>7.816386341038639E-5</v>
+        <v>7.816386341038639E-05</v>
       </c>
       <c r="J7">
-        <v>7.816386341038639E-4</v>
+        <v>0.0007816386341038639</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -2096,16 +2055,16 @@
         <v>21</v>
       </c>
       <c r="S7">
-        <v>-2.957987637108872E-2</v>
+        <v>-0.02957987637108872</v>
       </c>
       <c r="T7">
-        <v>0.97085332630341126</v>
+        <v>0.9708533263034113</v>
       </c>
       <c r="U7">
-        <v>0.95230553065076895</v>
+        <v>0.9523055306507689</v>
       </c>
       <c r="V7">
-        <v>0.98976237232423858</v>
+        <v>0.9897623723242386</v>
       </c>
       <c r="W7" t="s">
         <v>27</v>
@@ -2114,10 +2073,10 @@
         <v>43</v>
       </c>
       <c r="Y7">
-        <v>7.816386341038639E-5</v>
+        <v>7.816386341038639E-05</v>
       </c>
       <c r="Z7">
-        <v>7.816386341038639E-4</v>
+        <v>0.0007816386341038639</v>
       </c>
       <c r="AA7">
         <v>10</v>
@@ -2144,16 +2103,16 @@
         <v>21</v>
       </c>
       <c r="AI7">
-        <v>-2.957987637108872E-2</v>
+        <v>-0.02957987637108872</v>
       </c>
       <c r="AJ7">
-        <v>0.97085332630341126</v>
+        <v>0.9708533263034113</v>
       </c>
       <c r="AK7">
-        <v>0.95230553065076895</v>
+        <v>0.9523055306507689</v>
       </c>
       <c r="AL7">
-        <v>0.98976237232423858</v>
+        <v>0.9897623723242386</v>
       </c>
       <c r="AM7" t="s">
         <v>27</v>
@@ -2162,10 +2121,10 @@
         <v>43</v>
       </c>
       <c r="AO7">
-        <v>7.816386341038639E-5</v>
+        <v>7.816386341038639E-05</v>
       </c>
       <c r="AP7">
-        <v>7.816386341038639E-4</v>
+        <v>0.0007816386341038639</v>
       </c>
       <c r="AQ7">
         <v>10</v>
@@ -2192,16 +2151,16 @@
         <v>21</v>
       </c>
       <c r="AY7">
-        <v>-2.957987637108872E-2</v>
+        <v>-0.02957987637108872</v>
       </c>
       <c r="AZ7">
-        <v>0.97085332630341126</v>
+        <v>0.9708533263034113</v>
       </c>
       <c r="BA7">
-        <v>0.95230553065076895</v>
+        <v>0.9523055306507689</v>
       </c>
       <c r="BB7">
-        <v>0.98976237232423858</v>
+        <v>0.9897623723242386</v>
       </c>
       <c r="BC7" t="s">
         <v>27</v>
@@ -2210,10 +2169,10 @@
         <v>43</v>
       </c>
       <c r="BE7">
-        <v>7.816386341038639E-5</v>
+        <v>7.816386341038639E-05</v>
       </c>
       <c r="BF7">
-        <v>7.816386341038639E-4</v>
+        <v>0.0007816386341038639</v>
       </c>
       <c r="BG7">
         <v>10</v>
@@ -2237,7 +2196,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:65">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -2248,13 +2207,13 @@
         <v>0.1731498079459432</v>
       </c>
       <c r="D8">
-        <v>1.1890442200144189</v>
+        <v>1.189044220014419</v>
       </c>
       <c r="E8">
-        <v>1.1205874072896751</v>
+        <v>1.120587407289675</v>
       </c>
       <c r="F8">
-        <v>1.2616830672488719</v>
+        <v>1.261683067248872</v>
       </c>
       <c r="G8" t="s">
         <v>29</v>
@@ -2263,7 +2222,7 @@
         <v>45</v>
       </c>
       <c r="I8">
-        <v>5.4126544012444208E-14</v>
+        <v>5.412654401244421E-14</v>
       </c>
       <c r="J8">
         <v>5.412654401244421E-13</v>
@@ -2296,13 +2255,13 @@
         <v>0.1731498079459432</v>
       </c>
       <c r="T8">
-        <v>1.1890442200144189</v>
+        <v>1.189044220014419</v>
       </c>
       <c r="U8">
-        <v>1.1205874072896751</v>
+        <v>1.120587407289675</v>
       </c>
       <c r="V8">
-        <v>1.2616830672488719</v>
+        <v>1.261683067248872</v>
       </c>
       <c r="W8" t="s">
         <v>29</v>
@@ -2311,7 +2270,7 @@
         <v>45</v>
       </c>
       <c r="Y8">
-        <v>5.4126544012444208E-14</v>
+        <v>5.412654401244421E-14</v>
       </c>
       <c r="Z8">
         <v>5.412654401244421E-13</v>
@@ -2344,13 +2303,13 @@
         <v>0.1731498079459432</v>
       </c>
       <c r="AJ8">
-        <v>1.1890442200144189</v>
+        <v>1.189044220014419</v>
       </c>
       <c r="AK8">
-        <v>1.1205874072896751</v>
+        <v>1.120587407289675</v>
       </c>
       <c r="AL8">
-        <v>1.2616830672488719</v>
+        <v>1.261683067248872</v>
       </c>
       <c r="AM8" t="s">
         <v>29</v>
@@ -2359,7 +2318,7 @@
         <v>45</v>
       </c>
       <c r="AO8">
-        <v>5.4126544012444208E-14</v>
+        <v>5.412654401244421E-14</v>
       </c>
       <c r="AP8">
         <v>5.412654401244421E-13</v>
@@ -2392,13 +2351,13 @@
         <v>0.1731498079459432</v>
       </c>
       <c r="AZ8">
-        <v>1.1890442200144189</v>
+        <v>1.189044220014419</v>
       </c>
       <c r="BA8">
-        <v>1.1205874072896751</v>
+        <v>1.120587407289675</v>
       </c>
       <c r="BB8">
-        <v>1.2616830672488719</v>
+        <v>1.261683067248872</v>
       </c>
       <c r="BC8" t="s">
         <v>29</v>
@@ -2407,7 +2366,7 @@
         <v>45</v>
       </c>
       <c r="BE8">
-        <v>5.4126544012444208E-14</v>
+        <v>5.412654401244421E-14</v>
       </c>
       <c r="BF8">
         <v>5.412654401244421E-13</v>
@@ -2434,7 +2393,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:65">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -2442,16 +2401,16 @@
         <v>21</v>
       </c>
       <c r="C9">
-        <v>-2.9523766242088571E-2</v>
+        <v>-0.02952376624208857</v>
       </c>
       <c r="D9">
-        <v>0.97090780253711029</v>
+        <v>0.9709078025371103</v>
       </c>
       <c r="E9">
-        <v>0.95235774748802149</v>
+        <v>0.9523577474880215</v>
       </c>
       <c r="F9">
-        <v>0.98981917615921633</v>
+        <v>0.9898191761592163</v>
       </c>
       <c r="G9" t="s">
         <v>27</v>
@@ -2460,10 +2419,10 @@
         <v>43</v>
       </c>
       <c r="I9">
-        <v>8.0735251386457771E-5</v>
+        <v>8.073525138645777E-05</v>
       </c>
       <c r="J9">
-        <v>8.0735251386457774E-4</v>
+        <v>0.0008073525138645777</v>
       </c>
       <c r="K9">
         <v>10</v>
@@ -2490,16 +2449,16 @@
         <v>21</v>
       </c>
       <c r="S9">
-        <v>-2.9523766242088571E-2</v>
+        <v>-0.02952376624208857</v>
       </c>
       <c r="T9">
-        <v>0.97090780253711029</v>
+        <v>0.9709078025371103</v>
       </c>
       <c r="U9">
-        <v>0.95235774748802149</v>
+        <v>0.9523577474880215</v>
       </c>
       <c r="V9">
-        <v>0.98981917615921633</v>
+        <v>0.9898191761592163</v>
       </c>
       <c r="W9" t="s">
         <v>27</v>
@@ -2508,10 +2467,10 @@
         <v>43</v>
       </c>
       <c r="Y9">
-        <v>8.0735251386457771E-5</v>
+        <v>8.073525138645777E-05</v>
       </c>
       <c r="Z9">
-        <v>8.0735251386457774E-4</v>
+        <v>0.0008073525138645777</v>
       </c>
       <c r="AA9">
         <v>10</v>
@@ -2538,16 +2497,16 @@
         <v>21</v>
       </c>
       <c r="AI9">
-        <v>-2.9523766242088571E-2</v>
+        <v>-0.02952376624208857</v>
       </c>
       <c r="AJ9">
-        <v>0.97090780253711029</v>
+        <v>0.9709078025371103</v>
       </c>
       <c r="AK9">
-        <v>0.95235774748802149</v>
+        <v>0.9523577474880215</v>
       </c>
       <c r="AL9">
-        <v>0.98981917615921633</v>
+        <v>0.9898191761592163</v>
       </c>
       <c r="AM9" t="s">
         <v>27</v>
@@ -2556,10 +2515,10 @@
         <v>43</v>
       </c>
       <c r="AO9">
-        <v>8.0735251386457771E-5</v>
+        <v>8.073525138645777E-05</v>
       </c>
       <c r="AP9">
-        <v>8.0735251386457774E-4</v>
+        <v>0.0008073525138645777</v>
       </c>
       <c r="AQ9">
         <v>10</v>
@@ -2586,16 +2545,16 @@
         <v>21</v>
       </c>
       <c r="AY9">
-        <v>-2.9523766242088571E-2</v>
+        <v>-0.02952376624208857</v>
       </c>
       <c r="AZ9">
-        <v>0.97090780253711029</v>
+        <v>0.9709078025371103</v>
       </c>
       <c r="BA9">
-        <v>0.95235774748802149</v>
+        <v>0.9523577474880215</v>
       </c>
       <c r="BB9">
-        <v>0.98981917615921633</v>
+        <v>0.9898191761592163</v>
       </c>
       <c r="BC9" t="s">
         <v>27</v>
@@ -2604,10 +2563,10 @@
         <v>43</v>
       </c>
       <c r="BE9">
-        <v>8.0735251386457771E-5</v>
+        <v>8.073525138645777E-05</v>
       </c>
       <c r="BF9">
-        <v>8.0735251386457774E-4</v>
+        <v>0.0008073525138645777</v>
       </c>
       <c r="BG9">
         <v>10</v>
@@ -2631,7 +2590,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:65">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -2642,13 +2601,13 @@
         <v>0.6939949740077852</v>
       </c>
       <c r="D10">
-        <v>2.0016963058525712</v>
+        <v>2.001696305852571</v>
       </c>
       <c r="E10">
-        <v>1.1610016075110949</v>
+        <v>1.161001607511095</v>
       </c>
       <c r="F10">
-        <v>3.4511477632261092</v>
+        <v>3.451147763226109</v>
       </c>
       <c r="G10" t="s">
         <v>30</v>
@@ -2657,10 +2616,10 @@
         <v>46</v>
       </c>
       <c r="I10">
-        <v>1.031621014891636E-3</v>
+        <v>0.001031621014891636</v>
       </c>
       <c r="J10">
-        <v>1.0316210148916359E-2</v>
+        <v>0.01031621014891636</v>
       </c>
       <c r="K10">
         <v>10</v>
@@ -2687,16 +2646,16 @@
         <v>24</v>
       </c>
       <c r="S10">
-        <v>0.12773944435593579</v>
+        <v>0.1277394443559358</v>
       </c>
       <c r="T10">
-        <v>1.1362569059739409</v>
+        <v>1.136256905973941</v>
       </c>
       <c r="U10">
-        <v>1.0368399486997479</v>
+        <v>1.036839948699748</v>
       </c>
       <c r="V10">
-        <v>1.2452064158914351</v>
+        <v>1.245206415891435</v>
       </c>
       <c r="W10" t="s">
         <v>81</v>
@@ -2705,10 +2664,10 @@
         <v>92</v>
       </c>
       <c r="Y10">
-        <v>3.2616397399744018E-4</v>
+        <v>0.0003261639739974402</v>
       </c>
       <c r="Z10">
-        <v>3.2616397399744018E-3</v>
+        <v>0.003261639739974402</v>
       </c>
       <c r="AA10">
         <v>10</v>
@@ -2738,13 +2697,13 @@
         <v>0.6051406438167245</v>
       </c>
       <c r="AJ10">
-        <v>1.8315097812983749</v>
+        <v>1.831509781298375</v>
       </c>
       <c r="AK10">
         <v>1.166799036532649</v>
       </c>
       <c r="AL10">
-        <v>2.8748978821236428</v>
+        <v>2.874897882123643</v>
       </c>
       <c r="AM10" t="s">
         <v>104</v>
@@ -2753,10 +2712,10 @@
         <v>117</v>
       </c>
       <c r="AO10">
-        <v>5.4596008972014132E-4</v>
+        <v>0.0005459600897201413</v>
       </c>
       <c r="AP10">
-        <v>5.4596008972014132E-3</v>
+        <v>0.005459600897201413</v>
       </c>
       <c r="AQ10">
         <v>10</v>
@@ -2783,16 +2742,16 @@
         <v>24</v>
       </c>
       <c r="AY10">
-        <v>0.53313178661503902</v>
+        <v>0.533131786615039</v>
       </c>
       <c r="AZ10">
-        <v>1.7042613424252779</v>
+        <v>1.704261342425278</v>
       </c>
       <c r="BA10">
-        <v>1.1114292283346749</v>
+        <v>1.111429228334675</v>
       </c>
       <c r="BB10">
-        <v>2.6133078465438762</v>
+        <v>2.613307846543876</v>
       </c>
       <c r="BC10" t="s">
         <v>131</v>
@@ -2801,10 +2760,10 @@
         <v>141</v>
       </c>
       <c r="BE10">
-        <v>1.3162705841382859E-3</v>
+        <v>0.001316270584138286</v>
       </c>
       <c r="BF10">
-        <v>1.3162705841382859E-2</v>
+        <v>0.01316270584138286</v>
       </c>
       <c r="BG10">
         <v>10</v>
@@ -2828,7 +2787,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:65">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -2836,16 +2795,16 @@
         <v>21</v>
       </c>
       <c r="C11">
-        <v>-2.9211076408789179E-2</v>
+        <v>-0.02921107640878918</v>
       </c>
       <c r="D11">
-        <v>0.97121144300620454</v>
+        <v>0.9712114430062045</v>
       </c>
       <c r="E11">
         <v>0.9520990413150372</v>
       </c>
       <c r="F11">
-        <v>0.99070750635708738</v>
+        <v>0.9907075063570874</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
@@ -2854,10 +2813,10 @@
         <v>47</v>
       </c>
       <c r="I11">
-        <v>1.5323197019208421E-4</v>
+        <v>0.0001532319701920842</v>
       </c>
       <c r="J11">
-        <v>1.5323197019208421E-3</v>
+        <v>0.001532319701920842</v>
       </c>
       <c r="K11">
         <v>10</v>
@@ -2884,16 +2843,16 @@
         <v>21</v>
       </c>
       <c r="S11">
-        <v>-2.988079998719528E-2</v>
+        <v>-0.02988079998719528</v>
       </c>
       <c r="T11">
-        <v>0.97056121756316449</v>
+        <v>0.9705612175631645</v>
       </c>
       <c r="U11">
-        <v>0.95103124766523184</v>
+        <v>0.9510312476652318</v>
       </c>
       <c r="V11">
-        <v>0.99049224654843049</v>
+        <v>0.9904922465484305</v>
       </c>
       <c r="W11" t="s">
         <v>27</v>
@@ -2902,10 +2861,10 @@
         <v>93</v>
       </c>
       <c r="Y11">
-        <v>1.5285858002785579E-4</v>
+        <v>0.0001528585800278558</v>
       </c>
       <c r="Z11">
-        <v>1.5285858002785581E-3</v>
+        <v>0.001528585800278558</v>
       </c>
       <c r="AA11">
         <v>10</v>
@@ -2932,16 +2891,16 @@
         <v>21</v>
       </c>
       <c r="AI11">
-        <v>-2.793292293613726E-2</v>
+        <v>-0.02793292293613726</v>
       </c>
       <c r="AJ11">
-        <v>0.97245359394542441</v>
+        <v>0.9724535939454244</v>
       </c>
       <c r="AK11">
-        <v>0.95331282393016004</v>
+        <v>0.95331282393016</v>
       </c>
       <c r="AL11">
-        <v>0.99197867545590901</v>
+        <v>0.991978675455909</v>
       </c>
       <c r="AM11" t="s">
         <v>105</v>
@@ -2950,10 +2909,10 @@
         <v>118</v>
       </c>
       <c r="AO11">
-        <v>2.953174470419349E-4</v>
+        <v>0.0002953174470419349</v>
       </c>
       <c r="AP11">
-        <v>2.9531744704193491E-3</v>
+        <v>0.002953174470419349</v>
       </c>
       <c r="AQ11">
         <v>10</v>
@@ -2980,16 +2939,16 @@
         <v>21</v>
       </c>
       <c r="AY11">
-        <v>-2.8922480875495309E-2</v>
+        <v>-0.02892248087549531</v>
       </c>
       <c r="AZ11">
-        <v>0.97149177073926019</v>
+        <v>0.9714917707392602</v>
       </c>
       <c r="BA11">
-        <v>0.95276871817060227</v>
+        <v>0.9527687181706023</v>
       </c>
       <c r="BB11">
-        <v>0.99058275383586591</v>
+        <v>0.9905827538358659</v>
       </c>
       <c r="BC11" t="s">
         <v>27</v>
@@ -2998,10 +2957,10 @@
         <v>142</v>
       </c>
       <c r="BE11">
-        <v>1.2907687832582851E-4</v>
+        <v>0.0001290768783258285</v>
       </c>
       <c r="BF11">
-        <v>1.2907687832582849E-3</v>
+        <v>0.001290768783258285</v>
       </c>
       <c r="BG11">
         <v>10</v>
@@ -3025,7 +2984,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:65">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -3033,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="C12">
-        <v>0.18535516128299709</v>
+        <v>0.1853551612829971</v>
       </c>
       <c r="D12">
         <v>1.20364585262831</v>
       </c>
       <c r="E12">
-        <v>0.60652300542794624</v>
+        <v>0.6065230054279462</v>
       </c>
       <c r="F12">
         <v>2.388637076555939</v>
@@ -3051,10 +3010,10 @@
         <v>48</v>
       </c>
       <c r="I12">
-        <v>0.48603848762265472</v>
+        <v>0.4860384876226547</v>
       </c>
       <c r="J12">
-        <v>4.8603848762265471</v>
+        <v>4.860384876226547</v>
       </c>
       <c r="K12">
         <v>10</v>
@@ -3081,16 +3040,16 @@
         <v>24</v>
       </c>
       <c r="S12">
-        <v>4.4272712279290423E-2</v>
+        <v>0.04427271227929042</v>
       </c>
       <c r="T12">
         <v>1.045267373270504</v>
       </c>
       <c r="U12">
-        <v>0.93212611774991683</v>
+        <v>0.9321261177499168</v>
       </c>
       <c r="V12">
-        <v>1.1721416885745399</v>
+        <v>1.17214168857454</v>
       </c>
       <c r="W12" t="s">
         <v>82</v>
@@ -3099,10 +3058,10 @@
         <v>94</v>
       </c>
       <c r="Y12">
-        <v>0.31951604718596788</v>
+        <v>0.3195160471859679</v>
       </c>
       <c r="Z12">
-        <v>3.1951604718596789</v>
+        <v>3.195160471859679</v>
       </c>
       <c r="AA12">
         <v>10</v>
@@ -3129,16 +3088,16 @@
         <v>24</v>
       </c>
       <c r="AI12">
-        <v>0.21954043765748829</v>
+        <v>0.2195404376574883</v>
       </c>
       <c r="AJ12">
-        <v>1.2455042122101421</v>
+        <v>1.245504212210142</v>
       </c>
       <c r="AK12">
-        <v>0.70888777934526115</v>
+        <v>0.7088877793452611</v>
       </c>
       <c r="AL12">
-        <v>2.1883304915567772</v>
+        <v>2.188330491556777</v>
       </c>
       <c r="AM12" t="s">
         <v>106</v>
@@ -3150,7 +3109,7 @@
         <v>0.3156816176362377</v>
       </c>
       <c r="AP12">
-        <v>3.1568161763623772</v>
+        <v>3.156816176362377</v>
       </c>
       <c r="AQ12">
         <v>10</v>
@@ -3177,16 +3136,16 @@
         <v>24</v>
       </c>
       <c r="AY12">
-        <v>0.21682631861943541</v>
+        <v>0.2168263186194354</v>
       </c>
       <c r="AZ12">
         <v>1.242128348835676</v>
       </c>
       <c r="BA12">
-        <v>0.72742395114215519</v>
+        <v>0.7274239511421552</v>
       </c>
       <c r="BB12">
-        <v>2.1210228678320351</v>
+        <v>2.121022867832035</v>
       </c>
       <c r="BC12" t="s">
         <v>84</v>
@@ -3195,7 +3154,7 @@
         <v>143</v>
       </c>
       <c r="BE12">
-        <v>0.29657854818511781</v>
+        <v>0.2965785481851178</v>
       </c>
       <c r="BF12">
         <v>2.965785481851178</v>
@@ -3222,7 +3181,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:65">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -3230,16 +3189,16 @@
         <v>21</v>
       </c>
       <c r="C13">
-        <v>-3.378682971167718E-2</v>
+        <v>-0.03378682971167718</v>
       </c>
       <c r="D13">
-        <v>0.96677757092665961</v>
+        <v>0.9667775709266596</v>
       </c>
       <c r="E13">
-        <v>0.94319349956045651</v>
+        <v>0.9431934995604565</v>
       </c>
       <c r="F13">
-        <v>0.99095134994295297</v>
+        <v>0.990951349942953</v>
       </c>
       <c r="G13" t="s">
         <v>32</v>
@@ -3248,10 +3207,10 @@
         <v>49</v>
       </c>
       <c r="I13">
-        <v>4.2528525316193398E-4</v>
+        <v>0.000425285253161934</v>
       </c>
       <c r="J13">
-        <v>4.2528525316193402E-3</v>
+        <v>0.00425285253161934</v>
       </c>
       <c r="K13">
         <v>10</v>
@@ -3278,13 +3237,13 @@
         <v>21</v>
       </c>
       <c r="S13">
-        <v>-3.476343374270572E-2</v>
+        <v>-0.03476343374270572</v>
       </c>
       <c r="T13">
-        <v>0.96583387293841916</v>
+        <v>0.9658338729384192</v>
       </c>
       <c r="U13">
-        <v>0.94172513998577179</v>
+        <v>0.9417251399857718</v>
       </c>
       <c r="V13">
         <v>0.9905598040308452</v>
@@ -3296,10 +3255,10 @@
         <v>95</v>
       </c>
       <c r="Y13">
-        <v>3.9659419736029489E-4</v>
+        <v>0.0003965941973602949</v>
       </c>
       <c r="Z13">
-        <v>3.9659419736029497E-3</v>
+        <v>0.00396594197360295</v>
       </c>
       <c r="AA13">
         <v>10</v>
@@ -3326,16 +3285,16 @@
         <v>21</v>
       </c>
       <c r="AI13">
-        <v>-3.1864199433772798E-2</v>
+        <v>-0.0318641994337728</v>
       </c>
       <c r="AJ13">
-        <v>0.96863811475234229</v>
+        <v>0.9686381147523423</v>
       </c>
       <c r="AK13">
-        <v>0.94498358553051476</v>
+        <v>0.9449835855305148</v>
       </c>
       <c r="AL13">
-        <v>0.99288475664287001</v>
+        <v>0.99288475664287</v>
       </c>
       <c r="AM13" t="s">
         <v>107</v>
@@ -3344,10 +3303,10 @@
         <v>120</v>
       </c>
       <c r="AO13">
-        <v>9.0087306283306596E-4</v>
+        <v>0.000900873062833066</v>
       </c>
       <c r="AP13">
-        <v>9.0087306283306596E-3</v>
+        <v>0.00900873062833066</v>
       </c>
       <c r="AQ13">
         <v>10</v>
@@ -3374,16 +3333,16 @@
         <v>21</v>
       </c>
       <c r="AY13">
-        <v>-3.3192443179938053E-2</v>
+        <v>-0.03319244317993805</v>
       </c>
       <c r="AZ13">
-        <v>0.96735238130685697</v>
+        <v>0.967352381306857</v>
       </c>
       <c r="BA13">
-        <v>0.94420323734992384</v>
+        <v>0.9442032373499238</v>
       </c>
       <c r="BB13">
-        <v>0.99106907560119706</v>
+        <v>0.9910690756011971</v>
       </c>
       <c r="BC13" t="s">
         <v>32</v>
@@ -3392,10 +3351,10 @@
         <v>144</v>
       </c>
       <c r="BE13">
-        <v>4.1578479293772551E-4</v>
+        <v>0.0004157847929377255</v>
       </c>
       <c r="BF13">
-        <v>4.1578479293772549E-3</v>
+        <v>0.004157847929377255</v>
       </c>
       <c r="BG13">
         <v>10</v>
@@ -3419,7 +3378,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:65">
       <c r="A14" s="1">
         <v>1</v>
       </c>
@@ -3427,16 +3386,16 @@
         <v>25</v>
       </c>
       <c r="C14">
-        <v>0.83545788502054263</v>
+        <v>0.8354578850205426</v>
       </c>
       <c r="D14">
-        <v>2.3058696297638899</v>
+        <v>2.30586962976389</v>
       </c>
       <c r="E14">
-        <v>1.7994978572621689</v>
+        <v>1.799497857262169</v>
       </c>
       <c r="F14">
-        <v>2.9547324705109759</v>
+        <v>2.954732470510976</v>
       </c>
       <c r="G14" t="s">
         <v>33</v>
@@ -3445,10 +3404,10 @@
         <v>50</v>
       </c>
       <c r="I14">
-        <v>3.9874195131365307E-18</v>
+        <v>3.987419513136531E-18</v>
       </c>
       <c r="J14">
-        <v>3.9874195131365313E-17</v>
+        <v>3.987419513136531E-17</v>
       </c>
       <c r="K14">
         <v>10</v>
@@ -3475,16 +3434,16 @@
         <v>25</v>
       </c>
       <c r="S14">
-        <v>0.21661826818402349</v>
+        <v>0.2166182681840235</v>
       </c>
       <c r="T14">
-        <v>1.2418699503727519</v>
+        <v>1.241869950372752</v>
       </c>
       <c r="U14">
-        <v>1.1610801311724499</v>
+        <v>1.16108013117245</v>
       </c>
       <c r="V14">
-        <v>1.3282812548703931</v>
+        <v>1.328281254870393</v>
       </c>
       <c r="W14" t="s">
         <v>84</v>
@@ -3496,7 +3455,7 @@
         <v>1.087569009177756E-16</v>
       </c>
       <c r="Z14">
-        <v>1.0875690091777559E-15</v>
+        <v>1.087569009177756E-15</v>
       </c>
       <c r="AA14">
         <v>10</v>
@@ -3523,16 +3482,16 @@
         <v>25</v>
       </c>
       <c r="AI14">
-        <v>0.72291522596956725</v>
+        <v>0.7229152259695673</v>
       </c>
       <c r="AJ14">
-        <v>2.0604310860255701</v>
+        <v>2.06043108602557</v>
       </c>
       <c r="AK14">
         <v>1.644389259017353</v>
       </c>
       <c r="AL14">
-        <v>2.5817343654977658</v>
+        <v>2.581734365497766</v>
       </c>
       <c r="AM14" t="s">
         <v>108</v>
@@ -3541,7 +3500,7 @@
         <v>121</v>
       </c>
       <c r="AO14">
-        <v>1.5065270596582521E-16</v>
+        <v>1.506527059658252E-16</v>
       </c>
       <c r="AP14">
         <v>1.506527059658252E-15</v>
@@ -3577,10 +3536,10 @@
         <v>2.151966636935871</v>
       </c>
       <c r="BA14">
-        <v>1.7314135327821241</v>
+        <v>1.731413532782124</v>
       </c>
       <c r="BB14">
-        <v>2.6746703308041142</v>
+        <v>2.674670330804114</v>
       </c>
       <c r="BC14" t="s">
         <v>132</v>
@@ -3616,7 +3575,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:65">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -3624,16 +3583,16 @@
         <v>21</v>
       </c>
       <c r="C15">
-        <v>-2.9457195506418898E-2</v>
+        <v>-0.0294571955064189</v>
       </c>
       <c r="D15">
-        <v>0.97097243873520844</v>
+        <v>0.9709724387352084</v>
       </c>
       <c r="E15">
-        <v>0.95241769389808528</v>
+        <v>0.9524176938980853</v>
       </c>
       <c r="F15">
-        <v>0.98988866211076743</v>
+        <v>0.9898886621107674</v>
       </c>
       <c r="G15" t="s">
         <v>27</v>
@@ -3642,10 +3601,10 @@
         <v>43</v>
       </c>
       <c r="I15">
-        <v>8.4039506227113369E-5</v>
+        <v>8.403950622711337E-05</v>
       </c>
       <c r="J15">
-        <v>8.4039506227113364E-4</v>
+        <v>0.0008403950622711336</v>
       </c>
       <c r="K15">
         <v>10</v>
@@ -3672,16 +3631,16 @@
         <v>21</v>
       </c>
       <c r="S15">
-        <v>-2.949086256257645E-2</v>
+        <v>-0.02949086256257645</v>
       </c>
       <c r="T15">
-        <v>0.97093974950186424</v>
+        <v>0.9709397495018642</v>
       </c>
       <c r="U15">
-        <v>0.95238710168000729</v>
+        <v>0.9523871016800073</v>
       </c>
       <c r="V15">
-        <v>0.98985380576845416</v>
+        <v>0.9898538057684542</v>
       </c>
       <c r="W15" t="s">
         <v>27</v>
@@ -3690,10 +3649,10 @@
         <v>43</v>
       </c>
       <c r="Y15">
-        <v>8.237314214365891E-5</v>
+        <v>8.237314214365891E-05</v>
       </c>
       <c r="Z15">
-        <v>8.2373142143658904E-4</v>
+        <v>0.000823731421436589</v>
       </c>
       <c r="AA15">
         <v>10</v>
@@ -3720,16 +3679,16 @@
         <v>21</v>
       </c>
       <c r="AI15">
-        <v>-2.9393282035924641E-2</v>
+        <v>-0.02939328203592464</v>
       </c>
       <c r="AJ15">
-        <v>0.97103449893674254</v>
+        <v>0.9710344989367425</v>
       </c>
       <c r="AK15">
-        <v>0.95247905115080023</v>
+        <v>0.9524790511508002</v>
       </c>
       <c r="AL15">
-        <v>0.98995142936329594</v>
+        <v>0.9899514293632959</v>
       </c>
       <c r="AM15" t="s">
         <v>27</v>
@@ -3738,10 +3697,10 @@
         <v>43</v>
       </c>
       <c r="AO15">
-        <v>8.7036806877358925E-5</v>
+        <v>8.703680687735893E-05</v>
       </c>
       <c r="AP15">
-        <v>8.7036806877358931E-4</v>
+        <v>0.0008703680687735893</v>
       </c>
       <c r="AQ15">
         <v>10</v>
@@ -3768,16 +3727,16 @@
         <v>21</v>
       </c>
       <c r="AY15">
-        <v>-2.931117044885095E-2</v>
+        <v>-0.02931117044885095</v>
       </c>
       <c r="AZ15">
-        <v>0.97111423539415231</v>
+        <v>0.9711142353941523</v>
       </c>
       <c r="BA15">
-        <v>0.95255514372170258</v>
+        <v>0.9525551437217026</v>
       </c>
       <c r="BB15">
-        <v>0.99003492280830419</v>
+        <v>0.9900349228083042</v>
       </c>
       <c r="BC15" t="s">
         <v>27</v>
@@ -3786,10 +3745,10 @@
         <v>146</v>
       </c>
       <c r="BE15">
-        <v>9.1256491726115672E-5</v>
+        <v>9.125649172611567E-05</v>
       </c>
       <c r="BF15">
-        <v>9.1256491726115672E-4</v>
+        <v>0.0009125649172611567</v>
       </c>
       <c r="BG15">
         <v>10</v>
@@ -3813,7 +3772,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:65">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -3824,13 +3783,13 @@
         <v>-0.1161160412102292</v>
       </c>
       <c r="D16">
-        <v>0.89037189747002499</v>
+        <v>0.890371897470025</v>
       </c>
       <c r="E16">
-        <v>0.63659517922606657</v>
+        <v>0.6365951792260666</v>
       </c>
       <c r="F16">
-        <v>1.2453159270985441</v>
+        <v>1.245315927098544</v>
       </c>
       <c r="G16" t="s">
         <v>34</v>
@@ -3839,10 +3798,10 @@
         <v>51</v>
       </c>
       <c r="I16">
-        <v>0.37267356950971853</v>
+        <v>0.3726735695097185</v>
       </c>
       <c r="J16">
-        <v>3.7267356950971848</v>
+        <v>3.726735695097185</v>
       </c>
       <c r="K16">
         <v>10</v>
@@ -3869,13 +3828,13 @@
         <v>25</v>
       </c>
       <c r="S16">
-        <v>-3.7346090395535353E-2</v>
+        <v>-0.03734609039553535</v>
       </c>
       <c r="T16">
-        <v>0.96334267400141582</v>
+        <v>0.9633426740014158</v>
       </c>
       <c r="U16">
-        <v>0.88115103511310799</v>
+        <v>0.881151035113108</v>
       </c>
       <c r="V16">
         <v>1.053200950315031</v>
@@ -3887,10 +3846,10 @@
         <v>97</v>
       </c>
       <c r="Y16">
-        <v>0.28072880855863103</v>
+        <v>0.280728808558631</v>
       </c>
       <c r="Z16">
-        <v>2.8072880855863098</v>
+        <v>2.80728808558631</v>
       </c>
       <c r="AA16">
         <v>10</v>
@@ -3917,13 +3876,13 @@
         <v>25</v>
       </c>
       <c r="AI16">
-        <v>-8.0981065723872536E-2</v>
+        <v>-0.08098106572387254</v>
       </c>
       <c r="AJ16">
-        <v>0.92221115267991227</v>
+        <v>0.9222111526799123</v>
       </c>
       <c r="AK16">
-        <v>0.68376371678760639</v>
+        <v>0.6837637167876064</v>
       </c>
       <c r="AL16">
         <v>1.243811845008135</v>
@@ -3935,10 +3894,10 @@
         <v>122</v>
       </c>
       <c r="AO16">
-        <v>0.48564041710312961</v>
+        <v>0.4856404171031296</v>
       </c>
       <c r="AP16">
-        <v>4.8564041710312953</v>
+        <v>4.856404171031295</v>
       </c>
       <c r="AQ16">
         <v>10</v>
@@ -3965,13 +3924,13 @@
         <v>25</v>
       </c>
       <c r="AY16">
-        <v>-0.18486141573682199</v>
+        <v>-0.184861415736822</v>
       </c>
       <c r="AZ16">
-        <v>0.83121946980822348</v>
+        <v>0.8312194698082235</v>
       </c>
       <c r="BA16">
-        <v>0.61431371971109627</v>
+        <v>0.6143137197110963</v>
       </c>
       <c r="BB16">
         <v>1.124711665748239</v>
@@ -4010,7 +3969,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:65">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -4018,16 +3977,16 @@
         <v>21</v>
       </c>
       <c r="C17">
-        <v>-3.3796907010114882E-2</v>
+        <v>-0.03379690701011488</v>
       </c>
       <c r="D17">
-        <v>0.96676782846964349</v>
+        <v>0.9667678284696435</v>
       </c>
       <c r="E17">
-        <v>0.94383339764180496</v>
+        <v>0.943833397641805</v>
       </c>
       <c r="F17">
-        <v>0.99025954845329178</v>
+        <v>0.9902595484532918</v>
       </c>
       <c r="G17" t="s">
         <v>32</v>
@@ -4036,10 +3995,10 @@
         <v>52</v>
       </c>
       <c r="I17">
-        <v>2.878689247407931E-4</v>
+        <v>0.0002878689247407931</v>
       </c>
       <c r="J17">
-        <v>2.8786892474079312E-3</v>
+        <v>0.002878689247407931</v>
       </c>
       <c r="K17">
         <v>10</v>
@@ -4066,16 +4025,16 @@
         <v>21</v>
       </c>
       <c r="S17">
-        <v>-3.4036993359441527E-2</v>
+        <v>-0.03403699335944153</v>
       </c>
       <c r="T17">
-        <v>0.96653574857178226</v>
+        <v>0.9665357485717823</v>
       </c>
       <c r="U17">
-        <v>0.94361082227111182</v>
+        <v>0.9436108222711118</v>
       </c>
       <c r="V17">
-        <v>0.99001763356080918</v>
+        <v>0.9900176335608092</v>
       </c>
       <c r="W17" t="s">
         <v>32</v>
@@ -4084,10 +4043,10 @@
         <v>52</v>
       </c>
       <c r="Y17">
-        <v>2.5981923679842191E-4</v>
+        <v>0.0002598192367984219</v>
       </c>
       <c r="Z17">
-        <v>2.5981923679842191E-3</v>
+        <v>0.002598192367984219</v>
       </c>
       <c r="AA17">
         <v>10</v>
@@ -4114,16 +4073,16 @@
         <v>21</v>
       </c>
       <c r="AI17">
-        <v>-3.3710347745587357E-2</v>
+        <v>-0.03371034774558736</v>
       </c>
       <c r="AJ17">
-        <v>0.96685151480370612</v>
+        <v>0.9668515148037061</v>
       </c>
       <c r="AK17">
-        <v>0.94391539214901543</v>
+        <v>0.9439153921490154</v>
       </c>
       <c r="AL17">
-        <v>0.99034496042060993</v>
+        <v>0.9903449604206099</v>
       </c>
       <c r="AM17" t="s">
         <v>32</v>
@@ -4132,10 +4091,10 @@
         <v>52</v>
       </c>
       <c r="AO17">
-        <v>2.9833789309506809E-4</v>
+        <v>0.0002983378930950681</v>
       </c>
       <c r="AP17">
-        <v>2.9833789309506812E-3</v>
+        <v>0.002983378930950681</v>
       </c>
       <c r="AQ17">
         <v>10</v>
@@ -4162,16 +4121,16 @@
         <v>21</v>
       </c>
       <c r="AY17">
-        <v>-3.3709254327465382E-2</v>
+        <v>-0.03370925432746538</v>
       </c>
       <c r="AZ17">
-        <v>0.96685257197725172</v>
+        <v>0.9668525719772517</v>
       </c>
       <c r="BA17">
-        <v>0.94391542756240421</v>
+        <v>0.9439154275624042</v>
       </c>
       <c r="BB17">
-        <v>0.99034708898983947</v>
+        <v>0.9903470889898395</v>
       </c>
       <c r="BC17" t="s">
         <v>32</v>
@@ -4180,10 +4139,10 @@
         <v>52</v>
       </c>
       <c r="BE17">
-        <v>2.9865644526576578E-4</v>
+        <v>0.0002986564452657658</v>
       </c>
       <c r="BF17">
-        <v>2.986564452657658E-3</v>
+        <v>0.002986564452657658</v>
       </c>
       <c r="BG17">
         <v>10</v>
@@ -4207,7 +4166,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:65">
       <c r="A18" s="1">
         <v>1</v>
       </c>
@@ -4215,16 +4174,16 @@
         <v>24</v>
       </c>
       <c r="C18">
-        <v>0.68842327105238643</v>
+        <v>0.6884232710523864</v>
       </c>
       <c r="D18">
-        <v>1.9905744612088569</v>
+        <v>1.990574461208857</v>
       </c>
       <c r="E18">
         <v>1.153797524592671</v>
       </c>
       <c r="F18">
-        <v>3.4342131969955361</v>
+        <v>3.434213196995536</v>
       </c>
       <c r="G18" t="s">
         <v>35</v>
@@ -4233,10 +4192,10 @@
         <v>53</v>
       </c>
       <c r="I18">
-        <v>1.147919084413197E-3</v>
+        <v>0.001147919084413197</v>
       </c>
       <c r="J18">
-        <v>1.1479190844131969E-2</v>
+        <v>0.01147919084413197</v>
       </c>
       <c r="K18">
         <v>10</v>
@@ -4269,10 +4228,10 @@
         <v>1.136166947520999</v>
       </c>
       <c r="U18">
-        <v>1.0367279495019299</v>
+        <v>1.03672794950193</v>
       </c>
       <c r="V18">
-        <v>1.2451437556587079</v>
+        <v>1.245143755658708</v>
       </c>
       <c r="W18" t="s">
         <v>81</v>
@@ -4281,10 +4240,10 @@
         <v>92</v>
       </c>
       <c r="Y18">
-        <v>3.3039575458500118E-4</v>
+        <v>0.0003303957545850012</v>
       </c>
       <c r="Z18">
-        <v>3.3039575458500121E-3</v>
+        <v>0.003303957545850012</v>
       </c>
       <c r="AA18">
         <v>10</v>
@@ -4311,16 +4270,16 @@
         <v>24</v>
       </c>
       <c r="AI18">
-        <v>0.60140434224538886</v>
+        <v>0.6014043422453889</v>
       </c>
       <c r="AJ18">
-        <v>1.8246794764099279</v>
+        <v>1.824679476409928</v>
       </c>
       <c r="AK18">
-        <v>1.1620486898916069</v>
+        <v>1.162048689891607</v>
       </c>
       <c r="AL18">
-        <v>2.8651597997517388</v>
+        <v>2.865159799751739</v>
       </c>
       <c r="AM18" t="s">
         <v>110</v>
@@ -4329,10 +4288,10 @@
         <v>123</v>
       </c>
       <c r="AO18">
-        <v>5.9656447921695003E-4</v>
+        <v>0.00059656447921695</v>
       </c>
       <c r="AP18">
-        <v>5.9656447921695001E-3</v>
+        <v>0.0059656447921695</v>
       </c>
       <c r="AQ18">
         <v>10</v>
@@ -4365,7 +4324,7 @@
         <v>1.705506488209797</v>
       </c>
       <c r="BA18">
-        <v>1.1119917833560939</v>
+        <v>1.111991783356094</v>
       </c>
       <c r="BB18">
         <v>2.615803843933838</v>
@@ -4377,10 +4336,10 @@
         <v>148</v>
       </c>
       <c r="BE18">
-        <v>1.303890243295416E-3</v>
+        <v>0.001303890243295416</v>
       </c>
       <c r="BF18">
-        <v>1.303890243295416E-2</v>
+        <v>0.01303890243295416</v>
       </c>
       <c r="BG18">
         <v>10</v>
@@ -4404,7 +4363,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:65">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -4412,13 +4371,13 @@
         <v>25</v>
       </c>
       <c r="C19">
-        <v>0.80554362117444811</v>
+        <v>0.8055436211744481</v>
       </c>
       <c r="D19">
         <v>2.237912744956184</v>
       </c>
       <c r="E19">
-        <v>1.7310371361088079</v>
+        <v>1.731037136108808</v>
       </c>
       <c r="F19">
         <v>2.893209712008463</v>
@@ -4430,10 +4389,10 @@
         <v>54</v>
       </c>
       <c r="I19">
-        <v>6.5152751349621143E-16</v>
+        <v>6.515275134962114E-16</v>
       </c>
       <c r="J19">
-        <v>6.5152751349621139E-15</v>
+        <v>6.515275134962114E-15</v>
       </c>
       <c r="K19">
         <v>10</v>
@@ -4460,13 +4419,13 @@
         <v>25</v>
       </c>
       <c r="S19">
-        <v>0.20600910188627131</v>
+        <v>0.2060091018862713</v>
       </c>
       <c r="T19">
         <v>1.228764388018128</v>
       </c>
       <c r="U19">
-        <v>1.1442287563894249</v>
+        <v>1.144228756389425</v>
       </c>
       <c r="V19">
         <v>1.319545512932119</v>
@@ -4478,10 +4437,10 @@
         <v>98</v>
       </c>
       <c r="Y19">
-        <v>9.7175636064268977E-14</v>
+        <v>9.717563606426898E-14</v>
       </c>
       <c r="Z19">
-        <v>9.7175636064268974E-13</v>
+        <v>9.717563606426897E-13</v>
       </c>
       <c r="AA19">
         <v>10</v>
@@ -4508,7 +4467,7 @@
         <v>25</v>
       </c>
       <c r="AI19">
-        <v>0.69962077425057778</v>
+        <v>0.6996207742505778</v>
       </c>
       <c r="AJ19">
         <v>2.012989185373605</v>
@@ -4517,7 +4476,7 @@
         <v>1.594468787752839</v>
       </c>
       <c r="AL19">
-        <v>2.5413639273189812</v>
+        <v>2.541363927318981</v>
       </c>
       <c r="AM19" t="s">
         <v>111</v>
@@ -4556,13 +4515,13 @@
         <v>25</v>
       </c>
       <c r="AY19">
-        <v>0.75569961199767655</v>
+        <v>0.7556996119976765</v>
       </c>
       <c r="AZ19">
-        <v>2.1291005467119999</v>
+        <v>2.129100546712</v>
       </c>
       <c r="BA19">
-        <v>1.7089914353463671</v>
+        <v>1.708991435346367</v>
       </c>
       <c r="BB19">
         <v>2.652482068811894</v>
@@ -4574,10 +4533,10 @@
         <v>149</v>
       </c>
       <c r="BE19">
-        <v>8.2808798284166867E-19</v>
+        <v>8.280879828416687E-19</v>
       </c>
       <c r="BF19">
-        <v>8.2808798284166865E-18</v>
+        <v>8.280879828416687E-18</v>
       </c>
       <c r="BG19">
         <v>10</v>
@@ -4601,7 +4560,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:65">
       <c r="A20" s="1">
         <v>3</v>
       </c>
@@ -4609,16 +4568,16 @@
         <v>21</v>
       </c>
       <c r="C20">
-        <v>-2.904270037095652E-2</v>
+        <v>-0.02904270037095652</v>
       </c>
       <c r="D20">
-        <v>0.97137498550880852</v>
+        <v>0.9713749855088085</v>
       </c>
       <c r="E20">
-        <v>0.95225449249243199</v>
+        <v>0.952254492492432</v>
       </c>
       <c r="F20">
-        <v>0.99087940241955552</v>
+        <v>0.9908794024195555</v>
       </c>
       <c r="G20" t="s">
         <v>27</v>
@@ -4627,10 +4586,10 @@
         <v>47</v>
       </c>
       <c r="I20">
-        <v>1.6789945699047779E-4</v>
+        <v>0.0001678994569904778</v>
       </c>
       <c r="J20">
-        <v>1.6789945699047779E-3</v>
+        <v>0.001678994569904778</v>
       </c>
       <c r="K20">
         <v>10</v>
@@ -4657,16 +4616,16 @@
         <v>21</v>
       </c>
       <c r="S20">
-        <v>-2.982990614548817E-2</v>
+        <v>-0.02982990614548817</v>
       </c>
       <c r="T20">
-        <v>0.97061061440912522</v>
+        <v>0.9706106144091252</v>
       </c>
       <c r="U20">
-        <v>0.95107674879412452</v>
+        <v>0.9510767487941245</v>
       </c>
       <c r="V20">
-        <v>0.99054567993396347</v>
+        <v>0.9905456799339635</v>
       </c>
       <c r="W20" t="s">
         <v>27</v>
@@ -4675,10 +4634,10 @@
         <v>58</v>
       </c>
       <c r="Y20">
-        <v>1.572303804119166E-4</v>
+        <v>0.0001572303804119166</v>
       </c>
       <c r="Z20">
-        <v>1.5723038041191659E-3</v>
+        <v>0.001572303804119166</v>
       </c>
       <c r="AA20">
         <v>10</v>
@@ -4705,16 +4664,16 @@
         <v>21</v>
       </c>
       <c r="AI20">
-        <v>-2.7716749891703869E-2</v>
+        <v>-0.02771674989170387</v>
       </c>
       <c r="AJ20">
-        <v>0.97266383492279507</v>
+        <v>0.9726638349227951</v>
       </c>
       <c r="AK20">
-        <v>0.95351456041181171</v>
+        <v>0.9535145604118117</v>
       </c>
       <c r="AL20">
-        <v>0.99219768113254592</v>
+        <v>0.9921976811325459</v>
       </c>
       <c r="AM20" t="s">
         <v>112</v>
@@ -4723,10 +4682,10 @@
         <v>125</v>
       </c>
       <c r="AO20">
-        <v>3.2999890451943702E-4</v>
+        <v>0.000329998904519437</v>
       </c>
       <c r="AP20">
-        <v>3.2999890451943701E-3</v>
+        <v>0.00329998904519437</v>
       </c>
       <c r="AQ20">
         <v>10</v>
@@ -4753,16 +4712,16 @@
         <v>21</v>
       </c>
       <c r="AY20">
-        <v>-2.8642349225928239E-2</v>
+        <v>-0.02864234922592824</v>
       </c>
       <c r="AZ20">
         <v>0.9717639544533947</v>
       </c>
       <c r="BA20">
-        <v>0.95302919459209867</v>
+        <v>0.9530291945920987</v>
       </c>
       <c r="BB20">
-        <v>0.99086700442484887</v>
+        <v>0.9908670044248489</v>
       </c>
       <c r="BC20" t="s">
         <v>105</v>
@@ -4771,10 +4730,10 @@
         <v>142</v>
       </c>
       <c r="BE20">
-        <v>1.5075990817329539E-4</v>
+        <v>0.0001507599081732954</v>
       </c>
       <c r="BF20">
-        <v>1.507599081732954E-3</v>
+        <v>0.001507599081732954</v>
       </c>
       <c r="BG20">
         <v>10</v>
@@ -4798,7 +4757,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:65">
       <c r="A21" s="1">
         <v>1</v>
       </c>
@@ -4809,13 +4768,13 @@
         <v>0.1971348573202665</v>
       </c>
       <c r="D21">
-        <v>1.2179082734777551</v>
+        <v>1.217908273477755</v>
       </c>
       <c r="E21">
-        <v>0.61354124117488906</v>
+        <v>0.6135412411748891</v>
       </c>
       <c r="F21">
-        <v>2.4176053100605741</v>
+        <v>2.417605310060574</v>
       </c>
       <c r="G21" t="s">
         <v>37</v>
@@ -4824,10 +4783,10 @@
         <v>55</v>
       </c>
       <c r="I21">
-        <v>0.45893707444449539</v>
+        <v>0.4589370744444954</v>
       </c>
       <c r="J21">
-        <v>4.5893707444449543</v>
+        <v>4.589370744444954</v>
       </c>
       <c r="K21">
         <v>10</v>
@@ -4854,13 +4813,13 @@
         <v>24</v>
       </c>
       <c r="S21">
-        <v>4.525558482915068E-2</v>
+        <v>0.04525558482915068</v>
       </c>
       <c r="T21">
         <v>1.046295242928645</v>
       </c>
       <c r="U21">
-        <v>0.93303663096092726</v>
+        <v>0.9330366309609273</v>
       </c>
       <c r="V21">
         <v>1.173301989491724</v>
@@ -4872,10 +4831,10 @@
         <v>99</v>
       </c>
       <c r="Y21">
-        <v>0.30891834128633699</v>
+        <v>0.308918341286337</v>
       </c>
       <c r="Z21">
-        <v>3.0891834128633699</v>
+        <v>3.08918341286337</v>
       </c>
       <c r="AA21">
         <v>10</v>
@@ -4902,16 +4861,16 @@
         <v>24</v>
       </c>
       <c r="AI21">
-        <v>0.22691302322484019</v>
+        <v>0.2269130232248402</v>
       </c>
       <c r="AJ21">
         <v>1.254720731631223</v>
       </c>
       <c r="AK21">
-        <v>0.71411195015700479</v>
+        <v>0.7141119501570048</v>
       </c>
       <c r="AL21">
-        <v>2.2045900702810801</v>
+        <v>2.20459007028108</v>
       </c>
       <c r="AM21" t="s">
         <v>113</v>
@@ -4920,10 +4879,10 @@
         <v>126</v>
       </c>
       <c r="AO21">
-        <v>0.29973056636670531</v>
+        <v>0.2997305663667053</v>
       </c>
       <c r="AP21">
-        <v>2.9973056636670532</v>
+        <v>2.997305663667053</v>
       </c>
       <c r="AQ21">
         <v>10</v>
@@ -4950,10 +4909,10 @@
         <v>24</v>
       </c>
       <c r="AY21">
-        <v>0.22640912478874689</v>
+        <v>0.2264091247887469</v>
       </c>
       <c r="AZ21">
-        <v>1.2540886390854169</v>
+        <v>1.254088639085417</v>
       </c>
       <c r="BA21">
         <v>0.7344760897823257</v>
@@ -4968,7 +4927,7 @@
         <v>150</v>
       </c>
       <c r="BE21">
-        <v>0.27568542265869922</v>
+        <v>0.2756854226586992</v>
       </c>
       <c r="BF21">
         <v>2.756854226586992</v>
@@ -4995,7 +4954,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:65">
       <c r="A22" s="1">
         <v>2</v>
       </c>
@@ -5003,13 +4962,13 @@
         <v>25</v>
       </c>
       <c r="C22">
-        <v>-0.13040519870426109</v>
+        <v>-0.1304051987042611</v>
       </c>
       <c r="D22">
-        <v>0.87773969986548317</v>
+        <v>0.8777396998654832</v>
       </c>
       <c r="E22">
-        <v>0.62038858936730801</v>
+        <v>0.620388589367308</v>
       </c>
       <c r="F22">
         <v>1.241845826831945</v>
@@ -5021,7 +4980,7 @@
         <v>56</v>
       </c>
       <c r="I22">
-        <v>0.33304203819152961</v>
+        <v>0.3330420381915296</v>
       </c>
       <c r="J22">
         <v>3.330420381915296</v>
@@ -5051,16 +5010,16 @@
         <v>25</v>
       </c>
       <c r="S22">
-        <v>-4.7336505647686898E-2</v>
+        <v>-0.0473365056476869</v>
       </c>
       <c r="T22">
-        <v>0.95376639580518097</v>
+        <v>0.953766395805181</v>
       </c>
       <c r="U22">
-        <v>0.86766235542096515</v>
+        <v>0.8676623554209651</v>
       </c>
       <c r="V22">
-        <v>1.0484151260957479</v>
+        <v>1.048415126095748</v>
       </c>
       <c r="W22" t="s">
         <v>88</v>
@@ -5069,10 +5028,10 @@
         <v>100</v>
       </c>
       <c r="Y22">
-        <v>0.19750623614896259</v>
+        <v>0.1975062361489626</v>
       </c>
       <c r="Z22">
-        <v>1.9750623614896261</v>
+        <v>1.975062361489626</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -5099,16 +5058,16 @@
         <v>25</v>
       </c>
       <c r="AI22">
-        <v>-9.4193079249362183E-2</v>
+        <v>-0.09419307924936218</v>
       </c>
       <c r="AJ22">
         <v>0.9101070224947212</v>
       </c>
       <c r="AK22">
-        <v>0.66820523831278089</v>
+        <v>0.6682052383127809</v>
       </c>
       <c r="AL22">
-        <v>1.2395814113724291</v>
+        <v>1.239581411372429</v>
       </c>
       <c r="AM22" t="s">
         <v>114</v>
@@ -5117,10 +5076,10 @@
         <v>127</v>
       </c>
       <c r="AO22">
-        <v>0.43228975871648562</v>
+        <v>0.4322897587164856</v>
       </c>
       <c r="AP22">
-        <v>4.3228975871648556</v>
+        <v>4.322897587164856</v>
       </c>
       <c r="AQ22">
         <v>10</v>
@@ -5147,10 +5106,10 @@
         <v>25</v>
       </c>
       <c r="AY22">
-        <v>-0.21202221919189029</v>
+        <v>-0.2120222191918903</v>
       </c>
       <c r="AZ22">
-        <v>0.80894672322434058</v>
+        <v>0.8089467232243406</v>
       </c>
       <c r="BA22">
         <v>0.5952223057309699</v>
@@ -5165,10 +5124,10 @@
         <v>151</v>
       </c>
       <c r="BE22">
-        <v>7.5058665557557872E-2</v>
+        <v>0.07505866555755787</v>
       </c>
       <c r="BF22">
-        <v>0.75058665557557869</v>
+        <v>0.7505866555755787</v>
       </c>
       <c r="BG22">
         <v>10</v>
@@ -5192,7 +5151,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:65">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -5200,16 +5159,16 @@
         <v>21</v>
       </c>
       <c r="C23">
-        <v>-3.3527642161235299E-2</v>
+        <v>-0.0335276421612353</v>
       </c>
       <c r="D23">
         <v>0.9670281801130779</v>
       </c>
       <c r="E23">
-        <v>0.94343291533334084</v>
+        <v>0.9434329153333408</v>
       </c>
       <c r="F23">
-        <v>0.99121356265421323</v>
+        <v>0.9912135626542132</v>
       </c>
       <c r="G23" t="s">
         <v>32</v>
@@ -5218,10 +5177,10 @@
         <v>49</v>
       </c>
       <c r="I23">
-        <v>4.7214720586414687E-4</v>
+        <v>0.0004721472058641469</v>
       </c>
       <c r="J23">
-        <v>4.7214720586414684E-3</v>
+        <v>0.004721472058641468</v>
       </c>
       <c r="K23">
         <v>10</v>
@@ -5248,10 +5207,10 @@
         <v>21</v>
       </c>
       <c r="S23">
-        <v>-3.4802814041376987E-2</v>
+        <v>-0.03480281404137699</v>
       </c>
       <c r="T23">
-        <v>0.96579583886093756</v>
+        <v>0.9657958388609376</v>
       </c>
       <c r="U23">
         <v>0.9416874193154694</v>
@@ -5266,10 +5225,10 @@
         <v>95</v>
       </c>
       <c r="Y23">
-        <v>3.9074363909794718E-4</v>
+        <v>0.0003907436390979472</v>
       </c>
       <c r="Z23">
-        <v>3.9074363909794721E-3</v>
+        <v>0.003907436390979472</v>
       </c>
       <c r="AA23">
         <v>10</v>
@@ -5296,16 +5255,16 @@
         <v>21</v>
       </c>
       <c r="AI23">
-        <v>-3.1500832669735641E-2</v>
+        <v>-0.03150083266973564</v>
       </c>
       <c r="AJ23">
-        <v>0.96899014960463203</v>
+        <v>0.968990149604632</v>
       </c>
       <c r="AK23">
-        <v>0.94532220725441829</v>
+        <v>0.9453222072544183</v>
       </c>
       <c r="AL23">
-        <v>0.99325066398033535</v>
+        <v>0.9932506639803353</v>
       </c>
       <c r="AM23" t="s">
         <v>107</v>
@@ -5314,10 +5273,10 @@
         <v>120</v>
       </c>
       <c r="AO23">
-        <v>1.033481893048736E-3</v>
+        <v>0.001033481893048736</v>
       </c>
       <c r="AP23">
-        <v>1.033481893048736E-2</v>
+        <v>0.01033481893048736</v>
       </c>
       <c r="AQ23">
         <v>10</v>
@@ -5344,16 +5303,16 @@
         <v>21</v>
       </c>
       <c r="AY23">
-        <v>-3.2879864639262561E-2</v>
+        <v>-0.03287986463926256</v>
       </c>
       <c r="AZ23">
-        <v>0.96765480216519772</v>
+        <v>0.9676548021651977</v>
       </c>
       <c r="BA23">
-        <v>0.94449277240644214</v>
+        <v>0.9444927724064421</v>
       </c>
       <c r="BB23">
-        <v>0.99138484010593075</v>
+        <v>0.9913848401059308</v>
       </c>
       <c r="BC23" t="s">
         <v>138</v>
@@ -5362,10 +5321,10 @@
         <v>144</v>
       </c>
       <c r="BE23">
-        <v>4.7272727681507519E-4</v>
+        <v>0.0004727272768150752</v>
       </c>
       <c r="BF23">
-        <v>4.7272727681507516E-3</v>
+        <v>0.004727272768150752</v>
       </c>
       <c r="BG23">
         <v>10</v>
@@ -5389,7 +5348,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:65">
       <c r="A24" s="1">
         <v>1</v>
       </c>
@@ -5397,16 +5356,16 @@
         <v>24</v>
       </c>
       <c r="C24">
-        <v>0.70658437632672222</v>
+        <v>0.7065843763267222</v>
       </c>
       <c r="D24">
-        <v>2.0270557612198141</v>
+        <v>2.027055761219814</v>
       </c>
       <c r="E24">
-        <v>1.1624126640922909</v>
+        <v>1.162412664092291</v>
       </c>
       <c r="F24">
-        <v>3.5348505621306661</v>
+        <v>3.534850562130666</v>
       </c>
       <c r="G24" t="s">
         <v>39</v>
@@ -5415,10 +5374,10 @@
         <v>57</v>
       </c>
       <c r="I24">
-        <v>1.0643337096561221E-3</v>
+        <v>0.001064333709656122</v>
       </c>
       <c r="J24">
-        <v>1.064333709656122E-2</v>
+        <v>0.01064333709656122</v>
       </c>
       <c r="K24">
         <v>10</v>
@@ -5451,10 +5410,10 @@
         <v>1.14104978935946</v>
       </c>
       <c r="U24">
-        <v>1.0395282117835269</v>
+        <v>1.039528211783527</v>
       </c>
       <c r="V24">
-        <v>1.2524860865136369</v>
+        <v>1.252486086513637</v>
       </c>
       <c r="W24" t="s">
         <v>89</v>
@@ -5463,10 +5422,10 @@
         <v>101</v>
       </c>
       <c r="Y24">
-        <v>2.6483800886207821E-4</v>
+        <v>0.0002648380088620782</v>
       </c>
       <c r="Z24">
-        <v>2.6483800886207809E-3</v>
+        <v>0.002648380088620781</v>
       </c>
       <c r="AA24">
         <v>10</v>
@@ -5493,7 +5452,7 @@
         <v>24</v>
       </c>
       <c r="AI24">
-        <v>0.61028522207368208</v>
+        <v>0.6102852220736821</v>
       </c>
       <c r="AJ24">
         <v>1.840956405309834</v>
@@ -5502,7 +5461,7 @@
         <v>1.162685844512175</v>
       </c>
       <c r="AL24">
-        <v>2.9149064661342519</v>
+        <v>2.914906466134252</v>
       </c>
       <c r="AM24" t="s">
         <v>115</v>
@@ -5511,10 +5470,10 @@
         <v>128</v>
       </c>
       <c r="AO24">
-        <v>6.2460546995734645E-4</v>
+        <v>0.0006246054699573464</v>
       </c>
       <c r="AP24">
-        <v>6.2460546995734643E-3</v>
+        <v>0.006246054699573464</v>
       </c>
       <c r="AQ24">
         <v>10</v>
@@ -5541,13 +5500,13 @@
         <v>24</v>
       </c>
       <c r="AY24">
-        <v>0.54318113903434284</v>
+        <v>0.5431811390343428</v>
       </c>
       <c r="AZ24">
         <v>1.721474410502239</v>
       </c>
       <c r="BA24">
-        <v>1.1144173080380619</v>
+        <v>1.114417308038062</v>
       </c>
       <c r="BB24">
         <v>2.659214034670049</v>
@@ -5559,10 +5518,10 @@
         <v>152</v>
       </c>
       <c r="BE24">
-        <v>1.2929878090511739E-3</v>
+        <v>0.001292987809051174</v>
       </c>
       <c r="BF24">
-        <v>1.2929878090511739E-2</v>
+        <v>0.01292987809051174</v>
       </c>
       <c r="BG24">
         <v>10</v>
@@ -5586,7 +5545,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:65">
       <c r="A25" s="1">
         <v>2</v>
       </c>
@@ -5594,16 +5553,16 @@
         <v>21</v>
       </c>
       <c r="C25">
-        <v>-2.9577788895914552E-2</v>
+        <v>-0.02957778889591455</v>
       </c>
       <c r="D25">
-        <v>0.97085535293774294</v>
+        <v>0.9708553529377429</v>
       </c>
       <c r="E25">
-        <v>0.95141620263292037</v>
+        <v>0.9514162026329204</v>
       </c>
       <c r="F25">
-        <v>0.99069168017052589</v>
+        <v>0.9906916801705259</v>
       </c>
       <c r="G25" t="s">
         <v>27</v>
@@ -5612,10 +5571,10 @@
         <v>58</v>
       </c>
       <c r="I25">
-        <v>1.653367997923741E-4</v>
+        <v>0.0001653367997923741</v>
       </c>
       <c r="J25">
-        <v>1.653367997923741E-3</v>
+        <v>0.001653367997923741</v>
       </c>
       <c r="K25">
         <v>10</v>
@@ -5642,16 +5601,16 @@
         <v>21</v>
       </c>
       <c r="S25">
-        <v>-3.0226199312883381E-2</v>
+        <v>-0.03022619931288338</v>
       </c>
       <c r="T25">
-        <v>0.97022604426072767</v>
+        <v>0.9702260442607277</v>
       </c>
       <c r="U25">
-        <v>0.95036544478346152</v>
+        <v>0.9503654447834615</v>
       </c>
       <c r="V25">
-        <v>0.99050168767057944</v>
+        <v>0.9905016876705794</v>
       </c>
       <c r="W25" t="s">
         <v>90</v>
@@ -5660,10 +5619,10 @@
         <v>102</v>
       </c>
       <c r="Y25">
-        <v>1.669377250929073E-4</v>
+        <v>0.0001669377250929073</v>
       </c>
       <c r="Z25">
-        <v>1.669377250929073E-3</v>
+        <v>0.001669377250929073</v>
       </c>
       <c r="AA25">
         <v>10</v>
@@ -5690,16 +5649,16 @@
         <v>21</v>
       </c>
       <c r="AI25">
-        <v>-2.8002964952969011E-2</v>
+        <v>-0.02800296495296901</v>
       </c>
       <c r="AJ25">
-        <v>0.97238548371974576</v>
+        <v>0.9723854837197458</v>
       </c>
       <c r="AK25">
-        <v>0.95291082450933284</v>
+        <v>0.9529108245093328</v>
       </c>
       <c r="AL25">
-        <v>0.99225814696328218</v>
+        <v>0.9922581469632822</v>
       </c>
       <c r="AM25" t="s">
         <v>105</v>
@@ -5708,10 +5667,10 @@
         <v>118</v>
       </c>
       <c r="AO25">
-        <v>3.633501242520523E-4</v>
+        <v>0.0003633501242520523</v>
       </c>
       <c r="AP25">
-        <v>3.6335012425205231E-3</v>
+        <v>0.003633501242520523</v>
       </c>
       <c r="AQ25">
         <v>10</v>
@@ -5738,16 +5697,16 @@
         <v>21</v>
       </c>
       <c r="AY25">
-        <v>-2.959594759300422E-2</v>
+        <v>-0.02959594759300422</v>
       </c>
       <c r="AZ25">
-        <v>0.97083772362953413</v>
+        <v>0.9708377236295341</v>
       </c>
       <c r="BA25">
-        <v>0.95180064277313703</v>
+        <v>0.951800642773137</v>
       </c>
       <c r="BB25">
-        <v>0.99025556746427634</v>
+        <v>0.9902555674642763</v>
       </c>
       <c r="BC25" t="s">
         <v>27</v>
@@ -5756,10 +5715,10 @@
         <v>43</v>
       </c>
       <c r="BE25">
-        <v>1.183674664334903E-4</v>
+        <v>0.0001183674664334903</v>
       </c>
       <c r="BF25">
-        <v>1.1836746643349031E-3</v>
+        <v>0.001183674664334903</v>
       </c>
       <c r="BG25">
         <v>10</v>
@@ -5783,7 +5742,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:65">
       <c r="A26" s="1">
         <v>1</v>
       </c>
@@ -5791,13 +5750,13 @@
         <v>24</v>
       </c>
       <c r="C26">
-        <v>0.12613991902247229</v>
+        <v>0.1261399190224723</v>
       </c>
       <c r="D26">
         <v>1.134440887038846</v>
       </c>
       <c r="E26">
-        <v>0.56292321464620998</v>
+        <v>0.56292321464621</v>
       </c>
       <c r="F26">
         <v>2.286201905875068</v>
@@ -5809,10 +5768,10 @@
         <v>59</v>
       </c>
       <c r="I26">
-        <v>0.64288702032038891</v>
+        <v>0.6428870203203889</v>
       </c>
       <c r="J26">
-        <v>6.4288702032038891</v>
+        <v>6.428870203203889</v>
       </c>
       <c r="K26">
         <v>10</v>
@@ -5839,13 +5798,13 @@
         <v>24</v>
       </c>
       <c r="S26">
-        <v>4.1560944348972291E-2</v>
+        <v>0.04156094434897229</v>
       </c>
       <c r="T26">
         <v>1.042436690541046</v>
       </c>
       <c r="U26">
-        <v>0.92771700802401214</v>
+        <v>0.9277170080240121</v>
       </c>
       <c r="V26">
         <v>1.17134238608035</v>
@@ -5857,10 +5816,10 @@
         <v>103</v>
       </c>
       <c r="Y26">
-        <v>0.35850773544194181</v>
+        <v>0.3585077354419418</v>
       </c>
       <c r="Z26">
-        <v>3.5850773544194179</v>
+        <v>3.585077354419418</v>
       </c>
       <c r="AA26">
         <v>10</v>
@@ -5887,10 +5846,10 @@
         <v>24</v>
       </c>
       <c r="AI26">
-        <v>0.18257224071798739</v>
+        <v>0.1825722407179874</v>
       </c>
       <c r="AJ26">
-        <v>1.2003008584174479</v>
+        <v>1.200300858417448</v>
       </c>
       <c r="AK26">
         <v>0.6757749932221444</v>
@@ -5905,10 +5864,10 @@
         <v>129</v>
       </c>
       <c r="AO26">
-        <v>0.41299881557039242</v>
+        <v>0.4129988155703924</v>
       </c>
       <c r="AP26">
-        <v>4.1299881557039244</v>
+        <v>4.129988155703924</v>
       </c>
       <c r="AQ26">
         <v>10</v>
@@ -5935,16 +5894,16 @@
         <v>24</v>
       </c>
       <c r="AY26">
-        <v>0.18916650501376461</v>
+        <v>0.1891665050137646</v>
       </c>
       <c r="AZ26">
-        <v>1.2082421141050681</v>
+        <v>1.208242114105068</v>
       </c>
       <c r="BA26">
         <v>0.7010588756681253</v>
       </c>
       <c r="BB26">
-        <v>2.0823486542493499</v>
+        <v>2.08234865424935</v>
       </c>
       <c r="BC26" t="s">
         <v>140</v>
@@ -5953,10 +5912,10 @@
         <v>153</v>
       </c>
       <c r="BE26">
-        <v>0.37070326994530561</v>
+        <v>0.3707032699453056</v>
       </c>
       <c r="BF26">
-        <v>3.7070326994530549</v>
+        <v>3.707032699453055</v>
       </c>
       <c r="BG26">
         <v>10</v>
@@ -5980,7 +5939,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:65">
       <c r="A27" s="1">
         <v>2</v>
       </c>
@@ -5988,16 +5947,16 @@
         <v>21</v>
       </c>
       <c r="C27">
-        <v>-3.5411680666152009E-2</v>
+        <v>-0.03541168066615201</v>
       </c>
       <c r="D27">
-        <v>0.96520797699120575</v>
+        <v>0.9652079769912058</v>
       </c>
       <c r="E27">
-        <v>0.94130567606184135</v>
+        <v>0.9413056760618413</v>
       </c>
       <c r="F27">
-        <v>0.98971722208785495</v>
+        <v>0.989717222087855</v>
       </c>
       <c r="G27" t="s">
         <v>41</v>
@@ -6006,10 +5965,10 @@
         <v>60</v>
       </c>
       <c r="I27">
-        <v>2.7522493223248768E-4</v>
+        <v>0.0002752249322324877</v>
       </c>
       <c r="J27">
-        <v>2.7522493223248769E-3</v>
+        <v>0.002752249322324877</v>
       </c>
       <c r="K27">
         <v>10</v>
@@ -6036,16 +5995,16 @@
         <v>21</v>
       </c>
       <c r="S27">
-        <v>-3.5636695583969619E-2</v>
+        <v>-0.03563669558396962</v>
       </c>
       <c r="T27">
-        <v>0.96499081523082031</v>
+        <v>0.9649908152308203</v>
       </c>
       <c r="U27">
-        <v>0.94053998314008613</v>
+        <v>0.9405399831400861</v>
       </c>
       <c r="V27">
-        <v>0.99007728557260821</v>
+        <v>0.9900772855726082</v>
       </c>
       <c r="W27" t="s">
         <v>41</v>
@@ -6054,10 +6013,10 @@
         <v>60</v>
       </c>
       <c r="Y27">
-        <v>3.4795376059473581E-4</v>
+        <v>0.0003479537605947358</v>
       </c>
       <c r="Z27">
-        <v>3.4795376059473578E-3</v>
+        <v>0.003479537605947358</v>
       </c>
       <c r="AA27">
         <v>10</v>
@@ -6084,16 +6043,16 @@
         <v>21</v>
       </c>
       <c r="AI27">
-        <v>-3.352676617106537E-2</v>
+        <v>-0.03352676617106537</v>
       </c>
       <c r="AJ27">
-        <v>0.96702902722062878</v>
+        <v>0.9670290272206288</v>
       </c>
       <c r="AK27">
-        <v>0.94305695988908922</v>
+        <v>0.9430569598890892</v>
       </c>
       <c r="AL27">
-        <v>0.99161045330417352</v>
+        <v>0.9916104533041735</v>
       </c>
       <c r="AM27" t="s">
         <v>32</v>
@@ -6102,10 +6061,10 @@
         <v>130</v>
       </c>
       <c r="AO27">
-        <v>5.8094963897785282E-4</v>
+        <v>0.0005809496389778528</v>
       </c>
       <c r="AP27">
-        <v>5.809496389778528E-3</v>
+        <v>0.005809496389778528</v>
       </c>
       <c r="AQ27">
         <v>10</v>
@@ -6132,16 +6091,16 @@
         <v>21</v>
       </c>
       <c r="AY27">
-        <v>-3.539852498732559E-2</v>
+        <v>-0.03539852498732559</v>
       </c>
       <c r="AZ27">
-        <v>0.96522067504087727</v>
+        <v>0.9652206750408773</v>
       </c>
       <c r="BA27">
-        <v>0.94177634829729295</v>
+        <v>0.941776348297293</v>
       </c>
       <c r="BB27">
-        <v>0.98924861853960067</v>
+        <v>0.9892486185396007</v>
       </c>
       <c r="BC27" t="s">
         <v>41</v>
@@ -6150,10 +6109,10 @@
         <v>154</v>
       </c>
       <c r="BE27">
-        <v>2.0874150382540411E-4</v>
+        <v>0.0002087415038254041</v>
       </c>
       <c r="BF27">
-        <v>2.087415038254041E-3</v>
+        <v>0.002087415038254041</v>
       </c>
       <c r="BG27">
         <v>10</v>
@@ -6189,53 +6148,52 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AC16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29">
       <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2" t="s">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2" t="s">
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2" t="s">
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>4</v>
@@ -6322,8 +6280,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:29" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" hidden="1"/>
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -6412,7 +6370,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -6501,7 +6459,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -6590,185 +6548,185 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
+    <row r="7" spans="1:29">
+      <c r="A7" s="1">
         <v>1</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" t="s">
         <v>162</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" t="s">
         <v>174</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" t="s">
         <v>179</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" t="s">
         <v>81</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" t="s">
         <v>92</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" t="s">
         <v>187</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" t="s">
         <v>197</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" t="s">
         <v>202</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="N7" t="s">
         <v>24</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" t="s">
         <v>104</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="P7" t="s">
         <v>117</v>
       </c>
-      <c r="Q7" s="4" t="s">
+      <c r="Q7" t="s">
         <v>210</v>
       </c>
-      <c r="R7" s="4" t="s">
+      <c r="R7" t="s">
         <v>219</v>
       </c>
-      <c r="S7" s="4" t="s">
+      <c r="S7" t="s">
         <v>224</v>
       </c>
-      <c r="T7" s="4" t="s">
+      <c r="T7" t="s">
         <v>24</v>
       </c>
-      <c r="U7" s="4" t="s">
+      <c r="U7" t="s">
         <v>131</v>
       </c>
-      <c r="V7" s="4" t="s">
+      <c r="V7" t="s">
         <v>141</v>
       </c>
-      <c r="W7" s="4" t="s">
+      <c r="W7" t="s">
         <v>232</v>
       </c>
-      <c r="X7" s="4" t="s">
+      <c r="X7" t="s">
         <v>242</v>
       </c>
-      <c r="Y7" s="4" t="s">
+      <c r="Y7" t="s">
         <v>246</v>
       </c>
-      <c r="Z7" s="4" t="s">
+      <c r="Z7" t="s">
         <v>24</v>
       </c>
-      <c r="AA7" s="4" t="s">
+      <c r="AA7" t="s">
         <v>61</v>
       </c>
-      <c r="AB7" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC7" s="4" t="s">
+      <c r="AB7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
+    <row r="8" spans="1:29">
+      <c r="A8" s="1">
         <v>1</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" t="s">
         <v>163</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" t="s">
         <v>172</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" t="s">
         <v>180</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" t="s">
         <v>82</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" t="s">
         <v>94</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" t="s">
         <v>188</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" t="s">
         <v>172</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" t="s">
         <v>203</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="N8" t="s">
         <v>24</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="O8" t="s">
         <v>106</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="P8" t="s">
         <v>119</v>
       </c>
-      <c r="Q8" s="4" t="s">
+      <c r="Q8" t="s">
         <v>211</v>
       </c>
-      <c r="R8" s="4" t="s">
+      <c r="R8" t="s">
         <v>172</v>
       </c>
-      <c r="S8" s="4" t="s">
+      <c r="S8" t="s">
         <v>225</v>
       </c>
-      <c r="T8" s="4" t="s">
+      <c r="T8" t="s">
         <v>24</v>
       </c>
-      <c r="U8" s="4" t="s">
+      <c r="U8" t="s">
         <v>84</v>
       </c>
-      <c r="V8" s="4" t="s">
+      <c r="V8" t="s">
         <v>143</v>
       </c>
-      <c r="W8" s="4" t="s">
+      <c r="W8" t="s">
         <v>233</v>
       </c>
-      <c r="X8" s="4" t="s">
+      <c r="X8" t="s">
         <v>172</v>
       </c>
-      <c r="Y8" s="4" t="s">
+      <c r="Y8" t="s">
         <v>247</v>
       </c>
-      <c r="Z8" s="4" t="s">
+      <c r="Z8" t="s">
         <v>24</v>
       </c>
-      <c r="AA8" s="4" t="s">
+      <c r="AA8" t="s">
         <v>62</v>
       </c>
-      <c r="AB8" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC8" s="4" t="s">
+      <c r="AB8" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC8" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6857,7 +6815,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6946,7 +6904,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -7035,7 +6993,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -7124,7 +7082,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -7213,7 +7171,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -7302,7 +7260,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -7391,7 +7349,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -7481,18 +7439,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:AC16" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <filterColumn colId="18">
-      <filters>
-        <filter val="s_het_recessive_all"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="27">
-      <filters>
-        <filter val="selection regressions on [s_het_recessive_all]"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <mergeCells count="5">
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="H1:M1"/>
